--- a/FM-MN-07_Truck-83-2329.xlsx
+++ b/FM-MN-07_Truck-83-2329.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30508"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30514"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\From Iso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A227174-CB0E-46BC-827F-1509E795AE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF823440-615B-4DF9-B4DC-3D4AF16FA497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="83-2329" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'83-2329'!$A$1:$AG$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'83-2329'!$A$1:$AG$29</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>ผู้รับผิดชอบ  ………………........……..</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>Truck-83-2329</t>
+  </si>
+  <si>
+    <t>ตรวจสอบแบตเตอรี่ น้ำกลั่น ขั้วแบต และการยึดแน่น หากมีช่องตาแมว ให้สีแสดงสถานะอยู่ในเกณฑ์ปกติ</t>
   </si>
 </sst>
 </file>
@@ -224,7 +227,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -380,6 +383,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -388,12 +404,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -444,51 +457,59 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -517,15 +538,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2305465</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>3009487</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>96078</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3975653</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>284691</xdr:rowOff>
+      <xdr:colOff>4679675</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>52778</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -549,7 +570,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2578791" y="3475383"/>
+          <a:off x="3282813" y="3732143"/>
           <a:ext cx="1670188" cy="1116265"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -907,11 +928,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG27"/>
+  <dimension ref="A1:AG28"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="60.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="73.28515625" style="1" customWidth="1"/>
     <col min="3" max="33" width="3.7109375" style="1" customWidth="1"/>
     <col min="34" max="245" width="9" style="1" customWidth="1"/>
     <col min="246" max="246" width="7" style="1" customWidth="1"/>
@@ -1546,965 +1567,1011 @@
     <col min="16131" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:33" s="12" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A1" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="40"/>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="37" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="AC1" s="38"/>
-      <c r="AD1" s="38"/>
-      <c r="AE1" s="38"/>
-      <c r="AF1" s="38"/>
-      <c r="AG1" s="38"/>
-    </row>
-    <row r="2" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="39" t="s">
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="23"/>
+      <c r="AG1" s="23"/>
+    </row>
+    <row r="2" spans="1:33" s="12" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="40"/>
-    </row>
-    <row r="3" spans="1:33" s="13" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="16"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="14"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="14"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
-    </row>
-    <row r="4" spans="1:33" s="10" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="32" t="s">
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
+    </row>
+    <row r="3" spans="1:33" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="15"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="13"/>
+      <c r="AC3" s="13"/>
+      <c r="AD3" s="13"/>
+      <c r="AE3" s="13"/>
+      <c r="AF3" s="13"/>
+      <c r="AG3" s="13"/>
+    </row>
+    <row r="4" spans="1:33" s="9" customFormat="1" ht="18" customHeight="1">
+      <c r="A4" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="33"/>
-      <c r="AB4" s="33"/>
-      <c r="AC4" s="33"/>
-      <c r="AD4" s="33"/>
-      <c r="AE4" s="33"/>
-      <c r="AF4" s="33"/>
-      <c r="AG4" s="34"/>
-    </row>
-    <row r="5" spans="1:33" s="10" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="27"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="11">
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="37"/>
+    </row>
+    <row r="5" spans="1:33" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A5" s="25"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="10">
         <v>1</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>2</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <v>3</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <v>4</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <v>5</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="10">
         <v>6</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="10">
         <v>7</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="10">
         <v>8</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="10">
         <v>9</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="10">
         <v>10</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="10">
         <v>11</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="10">
         <v>12</v>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="10">
         <v>13</v>
       </c>
-      <c r="P5" s="11">
+      <c r="P5" s="10">
         <v>14</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="Q5" s="10">
         <v>15</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="10">
         <v>16</v>
       </c>
-      <c r="S5" s="11">
+      <c r="S5" s="10">
         <v>17</v>
       </c>
-      <c r="T5" s="11">
+      <c r="T5" s="10">
         <v>18</v>
       </c>
-      <c r="U5" s="11">
+      <c r="U5" s="10">
         <v>19</v>
       </c>
-      <c r="V5" s="11">
+      <c r="V5" s="10">
         <v>20</v>
       </c>
-      <c r="W5" s="11">
+      <c r="W5" s="10">
         <v>21</v>
       </c>
-      <c r="X5" s="11">
+      <c r="X5" s="10">
         <v>22</v>
       </c>
-      <c r="Y5" s="11">
+      <c r="Y5" s="10">
         <v>23</v>
       </c>
-      <c r="Z5" s="11">
+      <c r="Z5" s="10">
         <v>24</v>
       </c>
-      <c r="AA5" s="11">
+      <c r="AA5" s="10">
         <v>25</v>
       </c>
-      <c r="AB5" s="11">
+      <c r="AB5" s="10">
         <v>26</v>
       </c>
-      <c r="AC5" s="11">
+      <c r="AC5" s="10">
         <v>27</v>
       </c>
-      <c r="AD5" s="11">
+      <c r="AD5" s="10">
         <v>28</v>
       </c>
-      <c r="AE5" s="11">
+      <c r="AE5" s="10">
         <v>29</v>
       </c>
-      <c r="AF5" s="11">
+      <c r="AF5" s="10">
         <v>30</v>
       </c>
-      <c r="AG5" s="11">
+      <c r="AG5" s="10">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A6" s="12">
+    <row r="6" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A6" s="11">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20"/>
-      <c r="T6" s="20"/>
-      <c r="U6" s="20"/>
-      <c r="V6" s="20"/>
-      <c r="W6" s="20"/>
-      <c r="X6" s="20"/>
-      <c r="Y6" s="20"/>
-      <c r="Z6" s="20"/>
-      <c r="AA6" s="20"/>
-      <c r="AB6" s="20"/>
-      <c r="AC6" s="20"/>
-      <c r="AD6" s="20"/>
-      <c r="AE6" s="20"/>
-      <c r="AF6" s="20"/>
-      <c r="AG6" s="20"/>
-    </row>
-    <row r="7" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A7" s="9">
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+      <c r="AD6" s="19"/>
+      <c r="AE6" s="19"/>
+      <c r="AF6" s="19"/>
+      <c r="AG6" s="19"/>
+    </row>
+    <row r="7" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A7" s="8">
         <v>2</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
-      <c r="U7" s="20"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="20"/>
-      <c r="X7" s="20"/>
-      <c r="Y7" s="20"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="20"/>
-      <c r="AB7" s="20"/>
-      <c r="AC7" s="20"/>
-      <c r="AD7" s="20"/>
-      <c r="AE7" s="20"/>
-      <c r="AF7" s="20"/>
-      <c r="AG7" s="20"/>
-    </row>
-    <row r="8" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A8" s="9">
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
+      <c r="AA7" s="19"/>
+      <c r="AB7" s="19"/>
+      <c r="AC7" s="19"/>
+      <c r="AD7" s="19"/>
+      <c r="AE7" s="19"/>
+      <c r="AF7" s="19"/>
+      <c r="AG7" s="19"/>
+    </row>
+    <row r="8" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A8" s="8">
         <v>3</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="20"/>
-      <c r="V8" s="20"/>
-      <c r="W8" s="20"/>
-      <c r="X8" s="20"/>
-      <c r="Y8" s="20"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="20"/>
-      <c r="AC8" s="20"/>
-      <c r="AD8" s="20"/>
-      <c r="AE8" s="20"/>
-      <c r="AF8" s="20"/>
-      <c r="AG8" s="20"/>
-    </row>
-    <row r="9" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A9" s="9">
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="19"/>
+      <c r="W8" s="19"/>
+      <c r="X8" s="19"/>
+      <c r="Y8" s="19"/>
+      <c r="Z8" s="19"/>
+      <c r="AA8" s="19"/>
+      <c r="AB8" s="19"/>
+      <c r="AC8" s="19"/>
+      <c r="AD8" s="19"/>
+      <c r="AE8" s="19"/>
+      <c r="AF8" s="19"/>
+      <c r="AG8" s="19"/>
+    </row>
+    <row r="9" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A9" s="8">
         <v>4</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="20"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="20"/>
-      <c r="X9" s="20"/>
-      <c r="Y9" s="20"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="20"/>
-      <c r="AC9" s="20"/>
-      <c r="AD9" s="20"/>
-      <c r="AE9" s="20"/>
-      <c r="AF9" s="20"/>
-      <c r="AG9" s="20"/>
-    </row>
-    <row r="10" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A10" s="9">
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="19"/>
+      <c r="AA9" s="19"/>
+      <c r="AB9" s="19"/>
+      <c r="AC9" s="19"/>
+      <c r="AD9" s="19"/>
+      <c r="AE9" s="19"/>
+      <c r="AF9" s="19"/>
+      <c r="AG9" s="19"/>
+    </row>
+    <row r="10" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A10" s="8">
         <v>5</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="20"/>
-      <c r="V10" s="20"/>
-      <c r="W10" s="20"/>
-      <c r="X10" s="20"/>
-      <c r="Y10" s="20"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="20"/>
-      <c r="AB10" s="20"/>
-      <c r="AC10" s="20"/>
-      <c r="AD10" s="20"/>
-      <c r="AE10" s="20"/>
-      <c r="AF10" s="20"/>
-      <c r="AG10" s="20"/>
-    </row>
-    <row r="11" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A11" s="9">
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="19"/>
+      <c r="AA10" s="19"/>
+      <c r="AB10" s="19"/>
+      <c r="AC10" s="19"/>
+      <c r="AD10" s="19"/>
+      <c r="AE10" s="19"/>
+      <c r="AF10" s="19"/>
+      <c r="AG10" s="19"/>
+    </row>
+    <row r="11" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A11" s="8">
         <v>6</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="20"/>
-      <c r="U11" s="20"/>
-      <c r="V11" s="20"/>
-      <c r="W11" s="20"/>
-      <c r="X11" s="20"/>
-      <c r="Y11" s="20"/>
-      <c r="Z11" s="20"/>
-      <c r="AA11" s="20"/>
-      <c r="AB11" s="20"/>
-      <c r="AC11" s="20"/>
-      <c r="AD11" s="20"/>
-      <c r="AE11" s="20"/>
-      <c r="AF11" s="20"/>
-      <c r="AG11" s="20"/>
-    </row>
-    <row r="12" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A12" s="9">
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
+      <c r="AC11" s="19"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="19"/>
+      <c r="AF11" s="19"/>
+      <c r="AG11" s="19"/>
+    </row>
+    <row r="12" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A12" s="8">
         <v>7</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="20"/>
-      <c r="T12" s="20"/>
-      <c r="U12" s="20"/>
-      <c r="V12" s="20"/>
-      <c r="W12" s="20"/>
-      <c r="X12" s="20"/>
-      <c r="Y12" s="20"/>
-      <c r="Z12" s="20"/>
-      <c r="AA12" s="20"/>
-      <c r="AB12" s="20"/>
-      <c r="AC12" s="20"/>
-      <c r="AD12" s="20"/>
-      <c r="AE12" s="20"/>
-      <c r="AF12" s="20"/>
-      <c r="AG12" s="20"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="19"/>
+      <c r="AA12" s="19"/>
+      <c r="AB12" s="19"/>
+      <c r="AC12" s="19"/>
+      <c r="AD12" s="19"/>
+      <c r="AE12" s="19"/>
+      <c r="AF12" s="19"/>
+      <c r="AG12" s="19"/>
     </row>
     <row r="13" spans="1:33" ht="15.75" customHeight="1">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>8</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="21"/>
-      <c r="AF13" s="21"/>
-      <c r="AG13" s="21"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="21"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="21"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="20"/>
+      <c r="AD13" s="20"/>
+      <c r="AE13" s="20"/>
+      <c r="AF13" s="20"/>
+      <c r="AG13" s="20"/>
     </row>
     <row r="14" spans="1:33" ht="15.75" customHeight="1">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>9</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
-      <c r="V14" s="21"/>
-      <c r="W14" s="21"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="21"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="21"/>
-      <c r="AC14" s="21"/>
-      <c r="AD14" s="21"/>
-      <c r="AE14" s="21"/>
-      <c r="AF14" s="21"/>
-      <c r="AG14" s="21"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="20"/>
+      <c r="AD14" s="20"/>
+      <c r="AE14" s="20"/>
+      <c r="AF14" s="20"/>
+      <c r="AG14" s="20"/>
     </row>
     <row r="15" spans="1:33" ht="15.75" customHeight="1">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>10</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="21"/>
-      <c r="W15" s="21"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="21"/>
-      <c r="AA15" s="22"/>
-      <c r="AB15" s="21"/>
-      <c r="AC15" s="21"/>
-      <c r="AD15" s="21"/>
-      <c r="AE15" s="21"/>
-      <c r="AF15" s="21"/>
-      <c r="AG15" s="21"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20"/>
+      <c r="Y15" s="21"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="21"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="20"/>
+      <c r="AD15" s="20"/>
+      <c r="AE15" s="20"/>
+      <c r="AF15" s="20"/>
+      <c r="AG15" s="20"/>
     </row>
     <row r="16" spans="1:33" ht="15.75" customHeight="1">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>11</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="21"/>
-      <c r="R16" s="21"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="21"/>
-      <c r="V16" s="21"/>
-      <c r="W16" s="21"/>
-      <c r="X16" s="21"/>
-      <c r="Y16" s="22"/>
-      <c r="Z16" s="21"/>
-      <c r="AA16" s="22"/>
-      <c r="AB16" s="21"/>
-      <c r="AC16" s="21"/>
-      <c r="AD16" s="21"/>
-      <c r="AE16" s="21"/>
-      <c r="AF16" s="21"/>
-      <c r="AG16" s="21"/>
-    </row>
-    <row r="17" spans="1:33" ht="22.5" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="26"/>
-      <c r="R17" s="26"/>
-      <c r="S17" s="26"/>
-      <c r="T17" s="26"/>
-      <c r="U17" s="26"/>
-      <c r="V17" s="26"/>
-      <c r="W17" s="26"/>
-      <c r="X17" s="26"/>
-      <c r="Y17" s="36"/>
-      <c r="Z17" s="26"/>
-      <c r="AA17" s="36"/>
-      <c r="AB17" s="26"/>
-      <c r="AC17" s="26"/>
-      <c r="AD17" s="26"/>
-      <c r="AE17" s="26"/>
-      <c r="AF17" s="26"/>
-      <c r="AG17" s="26"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="21"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="21"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="20"/>
+      <c r="AD16" s="20"/>
+      <c r="AE16" s="20"/>
+      <c r="AF16" s="20"/>
+      <c r="AG16" s="20"/>
+    </row>
+    <row r="17" spans="1:33" ht="15.75" customHeight="1">
+      <c r="A17" s="40">
+        <v>12</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="21"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="21"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="20"/>
+      <c r="AD17" s="20"/>
+      <c r="AE17" s="20"/>
+      <c r="AF17" s="20"/>
+      <c r="AG17" s="20"/>
     </row>
     <row r="18" spans="1:33" ht="22.5" customHeight="1">
+      <c r="A18" s="7"/>
       <c r="B18" s="6"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="27"/>
-      <c r="M18" s="27"/>
-      <c r="N18" s="27"/>
-      <c r="O18" s="27"/>
-      <c r="P18" s="27"/>
-      <c r="Q18" s="27"/>
-      <c r="R18" s="27"/>
-      <c r="S18" s="27"/>
-      <c r="T18" s="27"/>
-      <c r="U18" s="27"/>
-      <c r="V18" s="27"/>
-      <c r="W18" s="27"/>
-      <c r="X18" s="27"/>
-      <c r="Y18" s="27"/>
-      <c r="Z18" s="27"/>
-      <c r="AA18" s="27"/>
-      <c r="AB18" s="27"/>
-      <c r="AC18" s="27"/>
-      <c r="AD18" s="27"/>
-      <c r="AE18" s="27"/>
-      <c r="AF18" s="27"/>
-      <c r="AG18" s="27"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="29"/>
+      <c r="W18" s="29"/>
+      <c r="X18" s="29"/>
+      <c r="Y18" s="32"/>
+      <c r="Z18" s="29"/>
+      <c r="AA18" s="32"/>
+      <c r="AB18" s="29"/>
+      <c r="AC18" s="29"/>
+      <c r="AD18" s="29"/>
+      <c r="AE18" s="29"/>
+      <c r="AF18" s="29"/>
+      <c r="AG18" s="29"/>
     </row>
     <row r="19" spans="1:33" ht="22.5" customHeight="1">
-      <c r="B19" s="6"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="28"/>
-      <c r="W19" s="28"/>
-      <c r="X19" s="28"/>
-      <c r="Y19" s="29"/>
-      <c r="Z19" s="28"/>
-      <c r="AA19" s="29"/>
-      <c r="AB19" s="28"/>
-      <c r="AC19" s="28"/>
-      <c r="AD19" s="28"/>
-      <c r="AE19" s="28"/>
-      <c r="AF19" s="28"/>
-      <c r="AG19" s="28"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="25"/>
+      <c r="W19" s="25"/>
+      <c r="X19" s="25"/>
+      <c r="Y19" s="25"/>
+      <c r="Z19" s="25"/>
+      <c r="AA19" s="25"/>
+      <c r="AB19" s="25"/>
+      <c r="AC19" s="25"/>
+      <c r="AD19" s="25"/>
+      <c r="AE19" s="25"/>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="25"/>
     </row>
     <row r="20" spans="1:33" ht="22.5" customHeight="1">
-      <c r="B20" s="6"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="27"/>
-      <c r="AA20" s="27"/>
-      <c r="AB20" s="27"/>
-      <c r="AC20" s="27"/>
-      <c r="AD20" s="27"/>
-      <c r="AE20" s="27"/>
-      <c r="AF20" s="27"/>
-      <c r="AG20" s="27"/>
-    </row>
-    <row r="21" spans="1:33" ht="19.5" customHeight="1">
-      <c r="B21" s="17" t="s">
+      <c r="B20" s="5"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
+      <c r="S20" s="24"/>
+      <c r="T20" s="24"/>
+      <c r="U20" s="24"/>
+      <c r="V20" s="24"/>
+      <c r="W20" s="24"/>
+      <c r="X20" s="24"/>
+      <c r="Y20" s="35"/>
+      <c r="Z20" s="24"/>
+      <c r="AA20" s="35"/>
+      <c r="AB20" s="24"/>
+      <c r="AC20" s="24"/>
+      <c r="AD20" s="24"/>
+      <c r="AE20" s="24"/>
+      <c r="AF20" s="24"/>
+      <c r="AG20" s="24"/>
+    </row>
+    <row r="21" spans="1:33" ht="22.5" customHeight="1">
+      <c r="B21" s="5"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="25"/>
+      <c r="W21" s="25"/>
+      <c r="X21" s="25"/>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="25"/>
+      <c r="AA21" s="25"/>
+      <c r="AB21" s="25"/>
+      <c r="AC21" s="25"/>
+      <c r="AD21" s="25"/>
+      <c r="AE21" s="25"/>
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="25"/>
+    </row>
+    <row r="22" spans="1:33" ht="19.5" customHeight="1">
+      <c r="B22" s="16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="242.25" customHeight="1">
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
-      <c r="S22" s="23"/>
-      <c r="T22" s="23"/>
-      <c r="U22" s="23"/>
-      <c r="V22" s="23"/>
-      <c r="W22" s="23"/>
-      <c r="X22" s="23"/>
-      <c r="Y22" s="23"/>
-      <c r="Z22" s="23"/>
-      <c r="AA22" s="23"/>
-      <c r="AB22" s="23"/>
-      <c r="AC22" s="23"/>
-      <c r="AD22" s="23"/>
-      <c r="AE22" s="23"/>
-      <c r="AF22" s="23"/>
-      <c r="AG22" s="23"/>
-    </row>
-    <row r="23" spans="1:33" ht="23.25" customHeight="1"/>
-    <row r="24" spans="1:33" ht="21" customHeight="1">
-      <c r="AA24" s="5"/>
-      <c r="AB24" s="5"/>
-      <c r="AC24" s="24"/>
-      <c r="AD24" s="25"/>
-      <c r="AE24" s="25"/>
-      <c r="AF24" s="25"/>
-      <c r="AG24" s="25"/>
-    </row>
-    <row r="25" spans="1:33" ht="29.25" customHeight="1">
-      <c r="AC25" s="35" t="s">
+    <row r="23" spans="1:33" ht="242.25" customHeight="1">
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="38"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="38"/>
+      <c r="V23" s="38"/>
+      <c r="W23" s="38"/>
+      <c r="X23" s="38"/>
+      <c r="Y23" s="38"/>
+      <c r="Z23" s="38"/>
+      <c r="AA23" s="38"/>
+      <c r="AB23" s="38"/>
+      <c r="AC23" s="38"/>
+      <c r="AD23" s="38"/>
+      <c r="AE23" s="38"/>
+      <c r="AF23" s="38"/>
+      <c r="AG23" s="38"/>
+    </row>
+    <row r="24" spans="1:33" ht="23.25" customHeight="1"/>
+    <row r="25" spans="1:33" ht="21" customHeight="1">
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="41"/>
+      <c r="AC25" s="41"/>
+      <c r="AD25" s="41"/>
+      <c r="AE25" s="41"/>
+      <c r="AF25" s="41"/>
+      <c r="AG25" s="41"/>
+    </row>
+    <row r="26" spans="1:33" ht="29.25" customHeight="1">
+      <c r="AB26" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="AD25" s="25"/>
-      <c r="AE25" s="25"/>
-      <c r="AF25" s="25"/>
-      <c r="AG25" s="25"/>
-    </row>
-    <row r="26" spans="1:33" ht="7.5" customHeight="1">
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" spans="1:33" ht="14.25" customHeight="1">
-      <c r="C27" s="3"/>
-      <c r="AG27" s="2" t="s">
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="31"/>
+      <c r="AE26" s="31"/>
+      <c r="AF26" s="31"/>
+      <c r="AG26" s="31"/>
+    </row>
+    <row r="27" spans="1:33" ht="7.5" customHeight="1">
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="1:33" ht="14.25" customHeight="1">
+      <c r="C28" s="2"/>
+      <c r="AB28" s="42" t="s">
         <v>6</v>
       </c>
+      <c r="AC28" s="42"/>
+      <c r="AD28" s="42"/>
+      <c r="AE28" s="42"/>
+      <c r="AF28" s="42"/>
+      <c r="AG28" s="42"/>
     </row>
   </sheetData>
-  <mergeCells count="71">
+  <mergeCells count="72">
+    <mergeCell ref="AB26:AG26"/>
+    <mergeCell ref="AB25:AG25"/>
+    <mergeCell ref="AB28:AG28"/>
+    <mergeCell ref="B23:AG23"/>
+    <mergeCell ref="T18:T19"/>
+    <mergeCell ref="V18:V19"/>
+    <mergeCell ref="AB18:AB19"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="AE18:AE19"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="W20:W21"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="Y20:Y21"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="O20:O21"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="S20:S21"/>
+    <mergeCell ref="U20:U21"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="S18:S19"/>
+    <mergeCell ref="U18:U19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="V20:V21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="AG18:AG19"/>
+    <mergeCell ref="AD20:AD21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="R20:R21"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="T20:T21"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="W18:W19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="AE20:AE21"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="Z20:Z21"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="AC18:AC19"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="AD18:AD19"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="AB20:AB21"/>
     <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="P19:P20"/>
-    <mergeCell ref="AG19:AG20"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="P20:P21"/>
+    <mergeCell ref="AG20:AG21"/>
     <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="Q20:Q21"/>
     <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="Z17:Z18"/>
-    <mergeCell ref="AF17:AF18"/>
-    <mergeCell ref="AC19:AC20"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AF18:AF19"/>
+    <mergeCell ref="AC20:AC21"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="AF19:AF20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="O17:O18"/>
-    <mergeCell ref="AC25:AG25"/>
-    <mergeCell ref="Q17:Q18"/>
-    <mergeCell ref="W17:W18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="AE19:AE20"/>
-    <mergeCell ref="Y17:Y18"/>
-    <mergeCell ref="AA17:AA18"/>
-    <mergeCell ref="Z19:Z20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="AC17:AC18"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="AD17:AD18"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="AB19:AB20"/>
-    <mergeCell ref="AD19:AD20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="R19:R20"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="T19:T20"/>
-    <mergeCell ref="X17:X18"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="S19:S20"/>
-    <mergeCell ref="U19:U20"/>
-    <mergeCell ref="AA19:AA20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="P17:P18"/>
-    <mergeCell ref="S17:S18"/>
-    <mergeCell ref="U17:U18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="V19:V20"/>
-    <mergeCell ref="X19:X20"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="AG17:AG18"/>
-    <mergeCell ref="B22:AG22"/>
-    <mergeCell ref="AC24:AG24"/>
-    <mergeCell ref="T17:T18"/>
-    <mergeCell ref="V17:V18"/>
-    <mergeCell ref="AB17:AB18"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="AE17:AE18"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="Y19:Y20"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="R17:R18"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="AF20:AF21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="O18:O19"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="80" orientation="landscape" horizontalDpi="4294967292" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="75" orientation="landscape" horizontalDpi="4294967292" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/FM-MN-07_Truck-83-2329.xlsx
+++ b/FM-MN-07_Truck-83-2329.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\From Iso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF823440-615B-4DF9-B4DC-3D4AF16FA497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2065C1-B747-4DF2-8278-5C12562EFEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="83-2329" sheetId="1" r:id="rId1"/>
@@ -457,16 +457,49 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -476,41 +509,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1568,80 +1568,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="12" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="22" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="AC1" s="23"/>
-      <c r="AD1" s="23"/>
-      <c r="AE1" s="23"/>
-      <c r="AF1" s="23"/>
-      <c r="AG1" s="23"/>
+      <c r="AC1" s="38"/>
+      <c r="AD1" s="38"/>
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="38"/>
     </row>
     <row r="2" spans="1:33" s="12" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="27"/>
-      <c r="AB2" s="26" t="s">
+      <c r="A2" s="40"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="40"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="AC2" s="27"/>
-      <c r="AD2" s="27"/>
-      <c r="AE2" s="27"/>
-      <c r="AF2" s="27"/>
-      <c r="AG2" s="27"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="40"/>
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="40"/>
     </row>
     <row r="3" spans="1:33" s="12" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="15"/>
@@ -1679,49 +1679,49 @@
       <c r="AG3" s="13"/>
     </row>
     <row r="4" spans="1:33" s="9" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="36"/>
-      <c r="V4" s="36"/>
-      <c r="W4" s="36"/>
-      <c r="X4" s="36"/>
-      <c r="Y4" s="36"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="36"/>
-      <c r="AB4" s="36"/>
-      <c r="AC4" s="36"/>
-      <c r="AD4" s="36"/>
-      <c r="AE4" s="36"/>
-      <c r="AF4" s="36"/>
-      <c r="AG4" s="37"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="34"/>
+      <c r="Y4" s="34"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="34"/>
+      <c r="AB4" s="34"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="34"/>
+      <c r="AE4" s="34"/>
+      <c r="AF4" s="34"/>
+      <c r="AG4" s="35"/>
     </row>
     <row r="5" spans="1:33" s="9" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="34"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="10">
         <v>1</v>
       </c>
@@ -2246,10 +2246,10 @@
       <c r="AG16" s="20"/>
     </row>
     <row r="17" spans="1:33" ht="15.75" customHeight="1">
-      <c r="A17" s="40">
+      <c r="A17" s="23">
         <v>12</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="22" t="s">
         <v>20</v>
       </c>
       <c r="C17" s="20"/>
@@ -2287,139 +2287,139 @@
     <row r="18" spans="1:33" ht="22.5" customHeight="1">
       <c r="A18" s="7"/>
       <c r="B18" s="6"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="29"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-      <c r="W18" s="29"/>
-      <c r="X18" s="29"/>
-      <c r="Y18" s="32"/>
-      <c r="Z18" s="29"/>
-      <c r="AA18" s="32"/>
-      <c r="AB18" s="29"/>
-      <c r="AC18" s="29"/>
-      <c r="AD18" s="29"/>
-      <c r="AE18" s="29"/>
-      <c r="AF18" s="29"/>
-      <c r="AG18" s="29"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="27"/>
+      <c r="W18" s="27"/>
+      <c r="X18" s="27"/>
+      <c r="Y18" s="36"/>
+      <c r="Z18" s="27"/>
+      <c r="AA18" s="36"/>
+      <c r="AB18" s="27"/>
+      <c r="AC18" s="27"/>
+      <c r="AD18" s="27"/>
+      <c r="AE18" s="27"/>
+      <c r="AF18" s="27"/>
+      <c r="AG18" s="27"/>
     </row>
     <row r="19" spans="1:33" ht="22.5" customHeight="1">
       <c r="B19" s="5"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="25"/>
-      <c r="P19" s="25"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="25"/>
-      <c r="S19" s="25"/>
-      <c r="T19" s="25"/>
-      <c r="U19" s="25"/>
-      <c r="V19" s="25"/>
-      <c r="W19" s="25"/>
-      <c r="X19" s="25"/>
-      <c r="Y19" s="25"/>
-      <c r="Z19" s="25"/>
-      <c r="AA19" s="25"/>
-      <c r="AB19" s="25"/>
-      <c r="AC19" s="25"/>
-      <c r="AD19" s="25"/>
-      <c r="AE19" s="25"/>
-      <c r="AF19" s="25"/>
-      <c r="AG19" s="25"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="28"/>
+      <c r="W19" s="28"/>
+      <c r="X19" s="28"/>
+      <c r="Y19" s="28"/>
+      <c r="Z19" s="28"/>
+      <c r="AA19" s="28"/>
+      <c r="AB19" s="28"/>
+      <c r="AC19" s="28"/>
+      <c r="AD19" s="28"/>
+      <c r="AE19" s="28"/>
+      <c r="AF19" s="28"/>
+      <c r="AG19" s="28"/>
     </row>
     <row r="20" spans="1:33" ht="22.5" customHeight="1">
       <c r="B20" s="5"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="24"/>
-      <c r="Y20" s="35"/>
-      <c r="Z20" s="24"/>
-      <c r="AA20" s="35"/>
-      <c r="AB20" s="24"/>
-      <c r="AC20" s="24"/>
-      <c r="AD20" s="24"/>
-      <c r="AE20" s="24"/>
-      <c r="AF20" s="24"/>
-      <c r="AG20" s="24"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="29"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="29"/>
+      <c r="AC20" s="29"/>
+      <c r="AD20" s="29"/>
+      <c r="AE20" s="29"/>
+      <c r="AF20" s="29"/>
+      <c r="AG20" s="29"/>
     </row>
     <row r="21" spans="1:33" ht="22.5" customHeight="1">
       <c r="B21" s="5"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="25"/>
-      <c r="P21" s="25"/>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="25"/>
-      <c r="S21" s="25"/>
-      <c r="T21" s="25"/>
-      <c r="U21" s="25"/>
-      <c r="V21" s="25"/>
-      <c r="W21" s="25"/>
-      <c r="X21" s="25"/>
-      <c r="Y21" s="25"/>
-      <c r="Z21" s="25"/>
-      <c r="AA21" s="25"/>
-      <c r="AB21" s="25"/>
-      <c r="AC21" s="25"/>
-      <c r="AD21" s="25"/>
-      <c r="AE21" s="25"/>
-      <c r="AF21" s="25"/>
-      <c r="AG21" s="25"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="28"/>
+      <c r="U21" s="28"/>
+      <c r="V21" s="28"/>
+      <c r="W21" s="28"/>
+      <c r="X21" s="28"/>
+      <c r="Y21" s="28"/>
+      <c r="Z21" s="28"/>
+      <c r="AA21" s="28"/>
+      <c r="AB21" s="28"/>
+      <c r="AC21" s="28"/>
+      <c r="AD21" s="28"/>
+      <c r="AE21" s="28"/>
+      <c r="AF21" s="28"/>
+      <c r="AG21" s="28"/>
     </row>
     <row r="22" spans="1:33" ht="19.5" customHeight="1">
       <c r="B22" s="16" t="s">
@@ -2427,75 +2427,131 @@
       </c>
     </row>
     <row r="23" spans="1:33" ht="242.25" customHeight="1">
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-      <c r="R23" s="38"/>
-      <c r="S23" s="38"/>
-      <c r="T23" s="38"/>
-      <c r="U23" s="38"/>
-      <c r="V23" s="38"/>
-      <c r="W23" s="38"/>
-      <c r="X23" s="38"/>
-      <c r="Y23" s="38"/>
-      <c r="Z23" s="38"/>
-      <c r="AA23" s="38"/>
-      <c r="AB23" s="38"/>
-      <c r="AC23" s="38"/>
-      <c r="AD23" s="38"/>
-      <c r="AE23" s="38"/>
-      <c r="AF23" s="38"/>
-      <c r="AG23" s="38"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="26"/>
+      <c r="S23" s="26"/>
+      <c r="T23" s="26"/>
+      <c r="U23" s="26"/>
+      <c r="V23" s="26"/>
+      <c r="W23" s="26"/>
+      <c r="X23" s="26"/>
+      <c r="Y23" s="26"/>
+      <c r="Z23" s="26"/>
+      <c r="AA23" s="26"/>
+      <c r="AB23" s="26"/>
+      <c r="AC23" s="26"/>
+      <c r="AD23" s="26"/>
+      <c r="AE23" s="26"/>
+      <c r="AF23" s="26"/>
+      <c r="AG23" s="26"/>
     </row>
     <row r="24" spans="1:33" ht="23.25" customHeight="1"/>
     <row r="25" spans="1:33" ht="21" customHeight="1">
       <c r="AA25" s="4"/>
-      <c r="AB25" s="41"/>
-      <c r="AC25" s="41"/>
-      <c r="AD25" s="41"/>
-      <c r="AE25" s="41"/>
-      <c r="AF25" s="41"/>
-      <c r="AG25" s="41"/>
+      <c r="AB25" s="42"/>
+      <c r="AC25" s="42"/>
+      <c r="AD25" s="42"/>
+      <c r="AE25" s="42"/>
+      <c r="AF25" s="42"/>
+      <c r="AG25" s="42"/>
     </row>
     <row r="26" spans="1:33" ht="29.25" customHeight="1">
-      <c r="AB26" s="31" t="s">
+      <c r="AB26" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="AC26" s="31"/>
-      <c r="AD26" s="31"/>
-      <c r="AE26" s="31"/>
-      <c r="AF26" s="31"/>
-      <c r="AG26" s="31"/>
+      <c r="AC26" s="24"/>
+      <c r="AD26" s="24"/>
+      <c r="AE26" s="24"/>
+      <c r="AF26" s="24"/>
+      <c r="AG26" s="24"/>
     </row>
     <row r="27" spans="1:33" ht="7.5" customHeight="1">
       <c r="D27" s="3"/>
     </row>
     <row r="28" spans="1:33" ht="14.25" customHeight="1">
       <c r="C28" s="2"/>
-      <c r="AB28" s="42" t="s">
+      <c r="AB28" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="AC28" s="42"/>
-      <c r="AD28" s="42"/>
-      <c r="AE28" s="42"/>
-      <c r="AF28" s="42"/>
-      <c r="AG28" s="42"/>
+      <c r="AC28" s="25"/>
+      <c r="AD28" s="25"/>
+      <c r="AE28" s="25"/>
+      <c r="AF28" s="25"/>
+      <c r="AG28" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="72">
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="P20:P21"/>
+    <mergeCell ref="AG20:AG21"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="Q20:Q21"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="AF18:AF19"/>
+    <mergeCell ref="AC20:AC21"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="AF20:AF21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="AC18:AC19"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="AD18:AD19"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="AB20:AB21"/>
+    <mergeCell ref="AA20:AA21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="S18:S19"/>
+    <mergeCell ref="U18:U19"/>
+    <mergeCell ref="V20:V21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="R20:R21"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="T20:T21"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="O20:O21"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="S20:S21"/>
+    <mergeCell ref="U20:U21"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="AG18:AG19"/>
+    <mergeCell ref="AD20:AD21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="W18:W19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="AE20:AE21"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="Z20:Z21"/>
     <mergeCell ref="AB26:AG26"/>
     <mergeCell ref="AB25:AG25"/>
     <mergeCell ref="AB28:AG28"/>
@@ -2512,62 +2568,6 @@
     <mergeCell ref="Y20:Y21"/>
     <mergeCell ref="L18:L19"/>
     <mergeCell ref="R18:R19"/>
-    <mergeCell ref="O20:O21"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="S20:S21"/>
-    <mergeCell ref="U20:U21"/>
-    <mergeCell ref="AA20:AA21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="N18:N19"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="U18:U19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="V20:V21"/>
-    <mergeCell ref="X20:X21"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="AG18:AG19"/>
-    <mergeCell ref="AD20:AD21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="R20:R21"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="T20:T21"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="W18:W19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="AE20:AE21"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="Z20:Z21"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="AC18:AC19"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="AD18:AD19"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="AB20:AB21"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="N20:N21"/>
-    <mergeCell ref="P20:P21"/>
-    <mergeCell ref="AG20:AG21"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="Q20:Q21"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="AF18:AF19"/>
-    <mergeCell ref="AC20:AC21"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="AF20:AF21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="O18:O19"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
